--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T12:55:00+00:00</t>
+    <t>2026-07-09T14:22:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="472">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T14:22:57+00:00</t>
+    <t>2026-07-10T07:56:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1057,10 +1057,7 @@
 This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
   </si>
   <si>
-    <t>The free/busy status of an appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/appointmentstatus</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sas/ValueSet/sas-valueset-appointment-status</t>
   </si>
   <si>
     <t>Appointment.cancelationReason</t>
@@ -1840,7 +1837,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.7578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -7025,11 +7022,9 @@
       <c r="X51" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>72</v>
@@ -7064,10 +7059,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7093,13 +7088,13 @@
         <v>211</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7125,11 +7120,11 @@
         <v>72</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>72</v>
@@ -7147,7 +7142,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -7164,10 +7159,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7193,13 +7188,13 @@
         <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7225,11 +7220,11 @@
         <v>72</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>72</v>
@@ -7247,7 +7242,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -7264,10 +7259,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7293,13 +7288,13 @@
         <v>211</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7325,11 +7320,11 @@
         <v>72</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>72</v>
@@ -7347,7 +7342,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -7364,10 +7359,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7393,13 +7388,13 @@
         <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7429,7 +7424,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>72</v>
@@ -7447,7 +7442,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7464,10 +7459,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7493,13 +7488,13 @@
         <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="N56" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7529,7 +7524,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>72</v>
@@ -7547,7 +7542,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -7564,10 +7559,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7593,13 +7588,13 @@
         <v>211</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="N57" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7628,11 +7623,11 @@
         <v>105</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>72</v>
       </c>
@@ -7649,7 +7644,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -7666,10 +7661,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7692,16 +7687,16 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7751,7 +7746,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -7768,10 +7763,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7794,16 +7789,16 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7853,7 +7848,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7870,10 +7865,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7899,10 +7894,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>253</v>
@@ -7955,7 +7950,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
@@ -7972,10 +7967,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7998,16 +7993,16 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8057,7 +8052,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -8074,10 +8069,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8100,16 +8095,16 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8159,7 +8154,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -8176,10 +8171,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8202,16 +8197,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8261,7 +8256,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -8278,10 +8273,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8304,16 +8299,16 @@
         <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8363,7 +8358,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -8380,10 +8375,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8406,16 +8401,16 @@
         <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="N65" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8465,7 +8460,7 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
@@ -8482,10 +8477,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8508,16 +8503,16 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8567,7 +8562,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -8584,10 +8579,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8613,13 +8608,13 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8669,7 +8664,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -8686,10 +8681,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8715,10 +8710,10 @@
         <v>139</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>253</v>
@@ -8771,7 +8766,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8788,14 +8783,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -8814,16 +8809,16 @@
         <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8873,7 +8868,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8890,10 +8885,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8916,13 +8911,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8973,7 +8968,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8985,15 +8980,15 @@
         <v>92</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9090,10 +9085,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9192,14 +9187,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9221,10 +9216,10 @@
         <v>124</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>171</v>
@@ -9279,7 +9274,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -9296,10 +9291,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9325,13 +9320,13 @@
         <v>211</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9360,11 +9355,11 @@
         <v>184</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>72</v>
       </c>
@@ -9381,7 +9376,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -9398,10 +9393,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9424,16 +9419,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="N75" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9483,7 +9478,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -9500,10 +9495,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9600,10 +9595,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9702,10 +9697,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9804,10 +9799,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9906,10 +9901,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10008,10 +10003,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10108,10 +10103,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10210,10 +10205,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10314,10 +10309,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10418,10 +10413,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10518,10 +10513,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10620,10 +10615,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10668,7 +10663,7 @@
         <v>72</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>72</v>
@@ -10724,10 +10719,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10828,10 +10823,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10876,7 +10871,7 @@
         <v>72</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>283</v>
@@ -10932,10 +10927,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11034,10 +11029,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11136,10 +11131,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11238,10 +11233,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11340,10 +11335,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11369,10 +11364,10 @@
         <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>253</v>
@@ -11404,11 +11399,11 @@
         <v>205</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>72</v>
       </c>
@@ -11425,7 +11420,7 @@
         <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>73</v>
@@ -11442,10 +11437,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11471,10 +11466,10 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>253</v>
@@ -11507,7 +11502,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>72</v>
@@ -11525,7 +11520,7 @@
         <v>72</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11542,10 +11537,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11571,10 +11566,10 @@
         <v>294</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>297</v>
@@ -11627,7 +11622,7 @@
         <v>72</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>73</v>
@@ -11644,10 +11639,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11673,13 +11668,13 @@
         <v>294</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11729,7 +11724,7 @@
         <v>72</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T07:56:32+00:00</t>
+    <t>2026-07-10T08:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T08:06:49+00:00</t>
+    <t>2026-07-13T17:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T17:37:40+00:00</t>
+    <t>2026-07-13T18:45:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T18:45:44+00:00</t>
+    <t>2026-07-15T08:24:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:24:19+00:00</t>
+    <t>2026-07-15T09:46:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T09:46:46+00:00</t>
+    <t>2026-07-15T12:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:12:36+00:00</t>
+    <t>2026-07-15T12:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:23:19+00:00</t>
+    <t>2026-07-15T13:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:30:57+00:00</t>
+    <t>2026-07-15T14:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:20:54+00:00</t>
+    <t>2026-07-15T14:44:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:44:09+00:00</t>
+    <t>2026-07-15T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:26:13+00:00</t>
+    <t>2026-07-15T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:58:30+00:00</t>
+    <t>2026-07-15T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T17:15:57+00:00</t>
+    <t>2026-07-16T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:32:04+00:00</t>
+    <t>2026-07-20T10:20:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T10:20:59+00:00</t>
+    <t>2026-07-20T14:00:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:00:59+00:00</t>
+    <t>2026-07-22T08:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:48:12+00:00</t>
+    <t>2026-07-22T09:17:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:17:02+00:00</t>
+    <t>2026-07-22T09:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:06+00:00</t>
+    <t>2026-07-22T12:21:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:08+00:00</t>
+    <t>2026-07-22T13:08:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:08:28+00:00</t>
+    <t>2026-07-22T13:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:46:01+00:00</t>
+    <t>2026-07-22T14:02:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:02:04+00:00</t>
+    <t>2026-07-22T14:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:55:39+00:00</t>
+    <t>2026-07-22T15:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:36:30+00:00</t>
+    <t>2026-07-22T16:29:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:29:14+00:00</t>
+    <t>2026-07-22T16:42:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:42:04+00:00</t>
+    <t>2026-07-23T08:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:48:51+00:00</t>
+    <t>2026-07-23T09:00:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:00:10+00:00</t>
+    <t>2026-07-28T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:01:02+00:00</t>
+    <t>2026-07-28T14:17:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:17:02+00:00</t>
+    <t>2026-09-09T13:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:38:12+00:00</t>
+    <t>2026-09-09T14:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-FrAppointmentSAS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:33:52+00:00</t>
+    <t>2026-09-09T14:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
